--- a/Result/profitability/8383.xlsx
+++ b/Result/profitability/8383.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7937500000000001</v>
+        <v>0.9087500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>27.7975</v>
+        <v>26.89875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8325</v>
+        <v>0.9025000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>26.09875</v>
+        <v>25.09625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0.71875</v>
+        <v>0.8337500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>24.13375</v>
+        <v>23.23375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6250000000000001</v>
+        <v>0.7787500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>21.43</v>
+        <v>21.05</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.28</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6112500000000001</v>
+        <v>0.7125000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>20.075</v>
+        <v>19.73375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.85</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4037500000000001</v>
+        <v>0.4162500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>15.82125</v>
+        <v>14.555</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.15</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2325000000000001</v>
+        <v>0.3050000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>13.6725</v>
+        <v>13.2125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8383</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1409</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1092</v>
+      </c>
+      <c r="E75" t="n">
+        <v>317</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="G75" t="n">
+        <v>201</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>14.24%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>69</v>
+      </c>
+      <c r="J75" t="n">
+        <v>269</v>
+      </c>
+      <c r="K75" t="n">
+        <v>182</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.9800000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>27.73875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.5800000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5576923076923077</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.680000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1406190294230035</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.153846153846154</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.040000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.119075597336467</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
